--- a/TestData/Input_TestData.xlsx
+++ b/TestData/Input_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Group1001_TestAutomation_mARCH\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD002FE-E6E7-4A4D-8B92-D1D33EB51ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDC5E28-B3C9-4709-B3FE-410D794A9833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="526" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="526" firstSheet="16" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Momentum Growth" sheetId="10" r:id="rId1"/>
@@ -32,7 +32,8 @@
     <sheet name="Growth Pathways" sheetId="5" r:id="rId17"/>
     <sheet name="Parity MYGA" sheetId="23" r:id="rId18"/>
     <sheet name="Clear Spring" sheetId="20" r:id="rId19"/>
-    <sheet name="Product_List" sheetId="24" r:id="rId20"/>
+    <sheet name="Control_PDF_GCP" sheetId="24" r:id="rId20"/>
+    <sheet name="Sheet1" sheetId="25" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Momentum Growth'!$A$1:$J$38</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6258" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6242" uniqueCount="821">
   <si>
     <t>Text_Flag</t>
   </si>
@@ -2137,21 +2138,9 @@
     <t>RSS70033005-RC</t>
   </si>
   <si>
-    <t>PS100027398-T</t>
-  </si>
-  <si>
     <t>PS10</t>
   </si>
   <si>
-    <t>PS100027405-T</t>
-  </si>
-  <si>
-    <t>PS100027426-T</t>
-  </si>
-  <si>
-    <t>PS100027433-T</t>
-  </si>
-  <si>
     <t>NJ GP070043771-RC</t>
   </si>
   <si>
@@ -2497,12 +2486,6 @@
     <t>5 - POLPG TAYLOR 0200071022</t>
   </si>
   <si>
-    <t>Test_XML Copy</t>
-  </si>
-  <si>
-    <t>Test_XML Copy Flag</t>
-  </si>
-  <si>
     <t>Control_PDF Flag</t>
   </si>
   <si>
@@ -2521,10 +2504,16 @@
     <t>Regression</t>
   </si>
   <si>
-    <t>Test_PDF Flag</t>
-  </si>
-  <si>
-    <t>Test_PDF Product Folder</t>
+    <t>Test_XML_Copy</t>
+  </si>
+  <si>
+    <t>Test_XML_Copy_Flag</t>
+  </si>
+  <si>
+    <t>Test_PDF_Product_Folder</t>
+  </si>
+  <si>
+    <t>Test_PDF_Flag</t>
   </si>
 </sst>
 </file>
@@ -2631,7 +2620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2781,11 +2770,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2836,7 +2834,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2846,6 +2843,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3200,1542 +3199,1542 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="43" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
-      <c r="A2" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="46" t="s">
+      <c r="A2" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="49" t="s">
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
     </row>
     <row r="3" spans="1:14" ht="15">
-      <c r="A3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="46" t="s">
+      <c r="A3" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="49" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
     </row>
     <row r="4" spans="1:14" ht="15">
-      <c r="A4" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="49" t="s">
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
     </row>
     <row r="5" spans="1:14" ht="15">
-      <c r="A5" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="46" t="s">
+      <c r="A5" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="49" t="s">
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46" t="s">
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
     </row>
     <row r="6" spans="1:14" ht="15">
-      <c r="A6" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="A6" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="49" t="s">
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46" t="s">
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
     </row>
     <row r="7" spans="1:14" ht="15">
-      <c r="A7" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="46" t="s">
+      <c r="A7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="49" t="s">
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
     </row>
     <row r="8" spans="1:14" ht="15">
-      <c r="A8" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="46" t="s">
+      <c r="A8" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="49" t="s">
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46" t="s">
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="15">
-      <c r="A9" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="46" t="s">
+      <c r="A9" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="49" t="s">
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46" t="s">
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
     </row>
     <row r="10" spans="1:14" ht="15">
-      <c r="A10" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="46" t="s">
+      <c r="A10" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="49" t="s">
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
     </row>
     <row r="11" spans="1:14" ht="15">
-      <c r="A11" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="46" t="s">
+      <c r="A11" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="49" t="s">
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
     </row>
     <row r="12" spans="1:14" ht="15">
-      <c r="A12" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="46" t="s">
+      <c r="A12" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="49" t="s">
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46" t="s">
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="15">
-      <c r="A13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="46" t="s">
+      <c r="A13" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="49" t="s">
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
     </row>
     <row r="14" spans="1:14" ht="15">
-      <c r="A14" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="46" t="s">
+      <c r="A14" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="49" t="s">
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="15">
-      <c r="A15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="46" t="s">
+      <c r="A15" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="49" t="s">
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46" t="s">
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
     </row>
     <row r="16" spans="1:14" ht="15">
-      <c r="A16" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="46" t="s">
+      <c r="A16" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="49" t="s">
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46" t="s">
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="15">
-      <c r="A17" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="46" t="s">
+      <c r="A17" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="49" t="s">
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
     </row>
     <row r="18" spans="1:14" ht="15">
-      <c r="A18" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="46" t="s">
+      <c r="A18" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="49" t="s">
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46" t="s">
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
     </row>
     <row r="19" spans="1:14" ht="15">
-      <c r="A19" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="46" t="s">
+      <c r="A19" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="49" t="s">
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46" t="s">
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
     </row>
     <row r="20" spans="1:14" ht="15">
-      <c r="A20" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="46" t="s">
+      <c r="A20" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="49" t="s">
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="15">
-      <c r="A21" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="46" t="s">
+      <c r="A21" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="49" t="s">
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
     </row>
     <row r="22" spans="1:14" ht="15">
-      <c r="A22" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="46" t="s">
+      <c r="A22" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="49" t="s">
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46" t="s">
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
     </row>
     <row r="23" spans="1:14" ht="15">
-      <c r="A23" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="46" t="s">
+      <c r="A23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="49" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
     </row>
     <row r="24" spans="1:14" ht="15">
-      <c r="A24" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="46" t="s">
+      <c r="A24" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="49" t="s">
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
     </row>
     <row r="25" spans="1:14" ht="15">
-      <c r="A25" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="46" t="s">
+      <c r="A25" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="49" t="s">
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46" t="s">
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
     </row>
     <row r="26" spans="1:14" ht="15">
-      <c r="A26" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="49" t="s">
+      <c r="A26" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49" t="s">
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46" t="s">
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
     </row>
     <row r="27" spans="1:14" ht="15">
-      <c r="A27" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="49" t="s">
+      <c r="A27" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49" t="s">
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
     </row>
     <row r="28" spans="1:14" ht="15">
-      <c r="A28" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="49" t="s">
+      <c r="A28" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49" t="s">
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46" t="s">
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
     </row>
     <row r="29" spans="1:14" ht="15">
-      <c r="A29" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="49" t="s">
+      <c r="A29" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49" t="s">
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46" t="s">
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
     </row>
     <row r="30" spans="1:14" ht="15">
-      <c r="A30" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="49" t="s">
+      <c r="A30" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49" t="s">
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:14" ht="15">
-      <c r="A31" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="49" t="s">
+      <c r="A31" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49" t="s">
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
     </row>
     <row r="32" spans="1:14" ht="15">
-      <c r="A32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="49" t="s">
+      <c r="A32" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49" t="s">
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46" t="s">
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
     </row>
     <row r="33" spans="1:14" ht="15">
-      <c r="A33" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="49" t="s">
+      <c r="A33" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="49" t="s">
+      <c r="D33" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49" t="s">
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:14" ht="15">
-      <c r="A34" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="49" t="s">
+      <c r="A34" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="D34" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49" t="s">
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
     </row>
     <row r="35" spans="1:14" ht="15">
-      <c r="A35" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="49" t="s">
+      <c r="A35" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="49" t="s">
+      <c r="D35" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49" t="s">
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46" t="s">
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
+      <c r="M35" s="45"/>
+      <c r="N35" s="45"/>
     </row>
     <row r="36" spans="1:14" ht="15">
-      <c r="A36" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="49" t="s">
+      <c r="A36" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="49" t="s">
+      <c r="D36" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49" t="s">
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46" t="s">
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
     </row>
     <row r="37" spans="1:14" ht="15">
-      <c r="A37" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="49" t="s">
+      <c r="A37" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="49" t="s">
+      <c r="D37" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49" t="s">
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
     </row>
     <row r="38" spans="1:14" ht="15">
-      <c r="A38" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="49" t="s">
+      <c r="A38" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="49" t="s">
+      <c r="D38" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49" t="s">
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46" t="s">
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
     </row>
     <row r="39" spans="1:14" ht="15">
-      <c r="A39" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="49" t="s">
+      <c r="A39" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="49" t="s">
+      <c r="D39" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="49" t="s">
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46" t="s">
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
     </row>
     <row r="40" spans="1:14" ht="15">
-      <c r="A40" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="49" t="s">
+      <c r="A40" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="49" t="s">
+      <c r="D40" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="49" t="s">
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M40" s="45"/>
+      <c r="N40" s="45"/>
     </row>
     <row r="41" spans="1:14" ht="15">
-      <c r="A41" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="49" t="s">
+      <c r="A41" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="D41" s="49" t="s">
+      <c r="D41" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="49" t="s">
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="46"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="45"/>
+      <c r="N41" s="45"/>
     </row>
     <row r="42" spans="1:14" ht="15">
-      <c r="A42" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="49" t="s">
+      <c r="A42" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="D42" s="49" t="s">
+      <c r="D42" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="49" t="s">
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46" t="s">
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
     </row>
     <row r="43" spans="1:14" ht="15">
-      <c r="A43" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="49" t="s">
+      <c r="A43" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="49" t="s">
+      <c r="D43" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="49" t="s">
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="45"/>
+      <c r="N43" s="45"/>
     </row>
     <row r="44" spans="1:14" ht="15">
-      <c r="A44" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="49" t="s">
+      <c r="A44" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="49" t="s">
+      <c r="D44" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="49" t="s">
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="45"/>
+      <c r="N44" s="45"/>
     </row>
     <row r="45" spans="1:14" ht="15">
-      <c r="A45" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="49" t="s">
+      <c r="A45" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="49" t="s">
+      <c r="D45" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="49" t="s">
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46" t="s">
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
+      <c r="M45" s="45"/>
+      <c r="N45" s="45"/>
     </row>
     <row r="46" spans="1:14" ht="15">
-      <c r="A46" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="49" t="s">
+      <c r="A46" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="49" t="s">
+      <c r="D46" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="49" t="s">
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46" t="s">
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="45"/>
     </row>
     <row r="47" spans="1:14" ht="15">
-      <c r="A47" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="49" t="s">
+      <c r="A47" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="D47" s="49" t="s">
+      <c r="D47" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="49" t="s">
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
     </row>
     <row r="48" spans="1:14" ht="15">
-      <c r="A48" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="49" t="s">
+      <c r="A48" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="D48" s="49" t="s">
+      <c r="D48" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="49" t="s">
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46" t="s">
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
     </row>
     <row r="49" spans="1:14" ht="15">
-      <c r="A49" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="49" t="s">
+      <c r="A49" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="D49" s="49" t="s">
+      <c r="D49" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="49" t="s">
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46" t="s">
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
+      <c r="M49" s="45"/>
+      <c r="N49" s="45"/>
     </row>
     <row r="50" spans="1:14" ht="15">
-      <c r="A50" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="49" t="s">
+      <c r="A50" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="D50" s="49" t="s">
+      <c r="D50" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="49" t="s">
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45"/>
     </row>
     <row r="51" spans="1:14" ht="15">
-      <c r="A51" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="49" t="s">
+      <c r="A51" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="49" t="s">
+      <c r="D51" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="49" t="s">
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" s="45"/>
+      <c r="N51" s="45"/>
     </row>
     <row r="52" spans="1:14" ht="15">
-      <c r="A52" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="50" t="s">
+      <c r="A52" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="D52" s="50" t="s">
+      <c r="D52" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="E52" s="50" t="s">
+      <c r="E52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="F52" s="50" t="s">
+      <c r="F52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G52" s="49" t="s">
+      <c r="G52" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="50" t="s">
+      <c r="H52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="I52" s="50" t="s">
+      <c r="I52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="J52" s="50" t="s">
+      <c r="J52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="K52" s="50" t="s">
+      <c r="K52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
+      <c r="L52" s="45"/>
+      <c r="M52" s="45"/>
+      <c r="N52" s="45"/>
     </row>
     <row r="53" spans="1:14" ht="15">
-      <c r="A53" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="46" t="s">
+      <c r="A53" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="46" t="s">
+      <c r="D53" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="49" t="s">
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H53" s="46"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="46"/>
-      <c r="M53" s="46" t="s">
+      <c r="H53" s="45"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="N53" s="46" t="s">
+      <c r="N53" s="45" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="46" t="s">
+      <c r="A54" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D54" s="46" t="s">
+      <c r="D54" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="46"/>
-      <c r="M54" s="46" t="s">
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="N54" s="46" t="s">
+      <c r="N54" s="45" t="s">
         <v>71</v>
       </c>
     </row>
@@ -4805,10 +4804,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15">
@@ -11774,10 +11773,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -12148,10 +12147,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -13514,10 +13513,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -14882,10 +14881,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -16344,7 +16343,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" style="21" bestFit="1" customWidth="1"/>
@@ -16358,7 +16357,7 @@
     <col min="9" max="9" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16400,10 +16399,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -17769,13 +17768,13 @@
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
     </row>
     <row r="51" spans="1:14" ht="15">
       <c r="A51" s="10" t="s">
@@ -17796,14 +17795,14 @@
         <v>537</v>
       </c>
       <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="2"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" s="45"/>
+      <c r="N51" s="45"/>
     </row>
     <row r="52" spans="1:14" ht="15">
       <c r="A52" s="10" t="s">
@@ -17813,10 +17812,10 @@
         <v>12</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>695</v>
+        <v>536</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>695</v>
+        <v>585</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>70</v>
@@ -17830,21 +17829,21 @@
       <c r="H52" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="I52" s="32" t="s">
+      <c r="I52" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="J52" s="32" t="s">
+      <c r="J52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="K52" s="32" t="s">
+      <c r="K52" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="L52" s="34"/>
-      <c r="M52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N52" s="42" t="s">
-        <v>696</v>
+      <c r="L52" s="49"/>
+      <c r="M52" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="N52" s="49" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="15">
@@ -17855,10 +17854,10 @@
         <v>12</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>697</v>
+        <v>538</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>697</v>
+        <v>586</v>
       </c>
       <c r="E53" s="36" t="s">
         <v>70</v>
@@ -17872,21 +17871,21 @@
       <c r="H53" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="I53" s="38" t="s">
+      <c r="I53" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="J53" s="38" t="s">
+      <c r="J53" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="K53" s="38" t="s">
+      <c r="K53" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="L53" s="34"/>
-      <c r="M53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N53" s="42" t="s">
-        <v>696</v>
+      <c r="L53" s="49"/>
+      <c r="M53" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="N53" s="49" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15">
@@ -17897,10 +17896,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>698</v>
+        <v>541</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>698</v>
+        <v>587</v>
       </c>
       <c r="E54" s="36" t="s">
         <v>70</v>
@@ -17914,63 +17913,21 @@
       <c r="H54" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="38" t="s">
+      <c r="I54" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="J54" s="38" t="s">
+      <c r="J54" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="K54" s="38" t="s">
+      <c r="K54" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="L54" s="34"/>
-      <c r="M54" s="2" t="s">
+      <c r="L54" s="49"/>
+      <c r="M54" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="N54" s="49" t="s">
         <v>71</v>
-      </c>
-      <c r="N54" s="42" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="15">
-      <c r="A55" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>699</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>699</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>537</v>
-      </c>
-      <c r="H55" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="I55" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="J55" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="L55" s="34"/>
-      <c r="M55" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N55" s="42" t="s">
-        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -17985,7 +17942,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -17996,17 +17953,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="16" customFormat="1">
-      <c r="A1" s="51" t="s">
-        <v>815</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>816</v>
+      <c r="A1" s="50" t="s">
+        <v>817</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>818</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E1"/>
       <c r="F1"/>
@@ -18033,20 +17990,37 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
+      <c r="C4" t="s">
+        <v>815</v>
+      </c>
       <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>816</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -18114,10 +18088,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -18128,10 +18102,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -18160,10 +18134,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -18192,10 +18166,10 @@
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -18220,10 +18194,10 @@
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -18248,10 +18222,10 @@
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -18276,10 +18250,10 @@
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -18304,10 +18278,10 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -18332,10 +18306,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -18360,10 +18334,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -18388,10 +18362,10 @@
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -18416,10 +18390,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -18444,10 +18418,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -18472,10 +18446,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -18500,10 +18474,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -18528,10 +18502,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -18556,10 +18530,10 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -18584,10 +18558,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -18612,10 +18586,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -18640,10 +18614,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -18668,10 +18642,10 @@
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -18696,10 +18670,10 @@
         <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -18724,10 +18698,10 @@
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -18780,10 +18754,10 @@
         <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -18808,10 +18782,10 @@
         <v>12</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -18836,10 +18810,10 @@
         <v>12</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -18864,10 +18838,10 @@
         <v>12</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -18892,10 +18866,10 @@
         <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -18920,10 +18894,10 @@
         <v>12</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -18976,10 +18950,10 @@
         <v>12</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -19004,10 +18978,10 @@
         <v>12</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -19032,10 +19006,10 @@
         <v>12</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -19060,10 +19034,10 @@
         <v>12</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -19088,10 +19062,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -19116,10 +19090,10 @@
         <v>12</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -19144,10 +19118,10 @@
         <v>12</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -19172,10 +19146,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -19200,10 +19174,10 @@
         <v>12</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -19228,10 +19202,10 @@
         <v>12</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -19256,10 +19230,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -19284,10 +19258,10 @@
         <v>12</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -19312,10 +19286,10 @@
         <v>12</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -19340,10 +19314,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -19368,10 +19342,10 @@
         <v>12</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -19396,10 +19370,10 @@
         <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -19424,10 +19398,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -19452,10 +19426,10 @@
         <v>12</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -19480,10 +19454,10 @@
         <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -19508,10 +19482,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -19536,10 +19510,10 @@
         <v>12</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="E52" s="26" t="s">
         <v>70</v>
@@ -19580,10 +19554,10 @@
         <v>12</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="E53" s="26" t="s">
         <v>70</v>
@@ -19643,1448 +19617,1448 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="43" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
+        <v>754</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>754</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="47"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>755</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>755</v>
+      </c>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" s="47"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>756</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>756</v>
+      </c>
+      <c r="E4" s="46"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="H4" s="47"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>757</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>757</v>
+      </c>
+      <c r="E5" s="46"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="H5" s="47"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>758</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>758</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="48"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="46" t="s">
+      <c r="H6" s="47"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B7" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C7" s="45" t="s">
         <v>759</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>759</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46" t="s">
+      <c r="E7" s="46"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H3" s="48"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="46" t="s">
+      <c r="H7" s="47"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B8" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C8" s="45" t="s">
         <v>760</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>760</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="E8" s="46"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="46" t="s">
+      <c r="H8" s="47"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B9" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C9" s="45" t="s">
         <v>761</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D9" s="45" t="s">
         <v>761</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46" t="s">
+      <c r="E9" s="46"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="46" t="s">
+      <c r="H9" s="47"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B10" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C10" s="45" t="s">
         <v>762</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D10" s="45" t="s">
         <v>762</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46" t="s">
+      <c r="E10" s="46"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="46" t="s">
+      <c r="H10" s="47"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B11" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C11" s="45" t="s">
         <v>763</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D11" s="45" t="s">
         <v>763</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46" t="s">
+      <c r="E11" s="46"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="46" t="s">
+      <c r="H11" s="47"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B12" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C12" s="45" t="s">
         <v>764</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D12" s="45" t="s">
         <v>764</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46" t="s">
+      <c r="E12" s="46"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="46" t="s">
+      <c r="H12" s="47"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B13" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C13" s="45" t="s">
         <v>765</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>765</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46" t="s">
+      <c r="E13" s="46"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H9" s="48"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="46" t="s">
+      <c r="H13" s="47"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B14" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C14" s="45" t="s">
         <v>766</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D14" s="45" t="s">
         <v>766</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46" t="s">
+      <c r="E14" s="46"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="46" t="s">
+      <c r="H14" s="47"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C15" s="45" t="s">
         <v>767</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>767</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46" t="s">
+      <c r="E15" s="46"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H11" s="48"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="46" t="s">
+      <c r="H15" s="47"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B16" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C16" s="45" t="s">
         <v>768</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D16" s="45" t="s">
         <v>768</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46" t="s">
+      <c r="E16" s="46"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="46" t="s">
+      <c r="H16" s="47"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B17" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C17" s="45" t="s">
         <v>769</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D17" s="45" t="s">
         <v>769</v>
       </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46" t="s">
+      <c r="E17" s="46"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="46" t="s">
+      <c r="H17" s="47"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B18" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C18" s="45" t="s">
         <v>770</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D18" s="45" t="s">
         <v>770</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46" t="s">
+      <c r="E18" s="46"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H14" s="48"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="46" t="s">
+      <c r="H18" s="47"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B19" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C19" s="45" t="s">
         <v>771</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D19" s="45" t="s">
         <v>771</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46" t="s">
+      <c r="E19" s="46"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="46" t="s">
+      <c r="H19" s="47"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B20" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C20" s="45" t="s">
         <v>772</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D20" s="45" t="s">
         <v>772</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46" t="s">
+      <c r="E20" s="46"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="46" t="s">
+      <c r="H20" s="47"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B21" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C21" s="45" t="s">
         <v>773</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D21" s="45" t="s">
         <v>773</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46" t="s">
+      <c r="E21" s="46"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="46" t="s">
+      <c r="H21" s="47"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>774</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>774</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46" t="s">
+      <c r="E22" s="46"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H18" s="48"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="46" t="s">
+      <c r="H22" s="47"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B23" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C23" s="45" t="s">
         <v>775</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D23" s="45" t="s">
         <v>775</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46" t="s">
+      <c r="E23" s="46"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H19" s="48"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="46" t="s">
+      <c r="H23" s="47"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B24" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C24" s="45" t="s">
         <v>776</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D24" s="45" t="s">
         <v>776</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46" t="s">
+      <c r="E24" s="46"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H20" s="48"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="46" t="s">
+      <c r="H24" s="47"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B25" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C25" s="45" t="s">
         <v>777</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D25" s="45" t="s">
         <v>777</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46" t="s">
+      <c r="E25" s="46"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H21" s="48"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="46" t="s">
+      <c r="H25" s="47"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B26" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C26" s="45" t="s">
         <v>778</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D26" s="45" t="s">
         <v>778</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46" t="s">
+      <c r="E26" s="46"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H22" s="48"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="46" t="s">
+      <c r="H26" s="47"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B27" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C27" s="45" t="s">
         <v>779</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D27" s="45" t="s">
         <v>779</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46" t="s">
+      <c r="E27" s="46"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H23" s="48"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="46" t="s">
+      <c r="H27" s="47"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B28" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C28" s="45" t="s">
         <v>780</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D28" s="45" t="s">
         <v>780</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46" t="s">
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H24" s="48"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="46" t="s">
+      <c r="H28" s="47"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B29" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C29" s="45" t="s">
         <v>781</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D29" s="45" t="s">
         <v>781</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46" t="s">
+      <c r="E29" s="46"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H25" s="48"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="46" t="s">
+      <c r="H29" s="47"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B30" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C30" s="45" t="s">
         <v>782</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D30" s="45" t="s">
         <v>782</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46" t="s">
+      <c r="E30" s="46"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H26" s="48"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="46" t="s">
+      <c r="H30" s="47"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B31" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C31" s="45" t="s">
         <v>783</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D31" s="45" t="s">
         <v>783</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46" t="s">
+      <c r="E31" s="46"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="48"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="46" t="s">
+      <c r="H31" s="47"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="B32" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C32" s="45" t="s">
         <v>784</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D32" s="45" t="s">
         <v>784</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46" t="s">
+      <c r="E32" s="46"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H28" s="48"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="46" t="s">
+      <c r="H32" s="47"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B33" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C33" s="45" t="s">
         <v>785</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D33" s="45" t="s">
         <v>785</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46" t="s">
+      <c r="E33" s="46"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H29" s="48"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="46" t="s">
+      <c r="H33" s="47"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="46" t="s">
+      <c r="B34" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C34" s="45" t="s">
         <v>786</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D34" s="45" t="s">
         <v>786</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46" t="s">
+      <c r="E34" s="46"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H30" s="48"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="46" t="s">
+      <c r="H34" s="47"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B35" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C35" s="45" t="s">
         <v>787</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D35" s="45" t="s">
         <v>787</v>
       </c>
-      <c r="E31" s="47"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46" t="s">
+      <c r="E35" s="46"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H31" s="48"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="46" t="s">
+      <c r="H35" s="47"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M35" s="45"/>
+      <c r="N35" s="45"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B36" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>788</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>788</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46" t="s">
+      <c r="E36" s="46"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H32" s="48"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="46" t="s">
+      <c r="H36" s="47"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B37" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C37" s="45" t="s">
         <v>789</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D37" s="45" t="s">
         <v>789</v>
       </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46" t="s">
+      <c r="E37" s="46"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H33" s="48"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="46" t="s">
+      <c r="H37" s="47"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="46" t="s">
+      <c r="B38" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C38" s="45" t="s">
         <v>790</v>
       </c>
-      <c r="D34" s="46" t="s">
+      <c r="D38" s="45" t="s">
         <v>790</v>
       </c>
-      <c r="E34" s="47"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46" t="s">
+      <c r="E38" s="46"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H34" s="48"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="46" t="s">
+      <c r="H38" s="47"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B39" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="46" t="s">
+      <c r="C39" s="45" t="s">
         <v>791</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D39" s="45" t="s">
         <v>791</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46" t="s">
+      <c r="E39" s="46"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H35" s="48"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="46" t="s">
+      <c r="H39" s="47"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B40" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C40" s="45" t="s">
         <v>792</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D40" s="45" t="s">
         <v>792</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46" t="s">
+      <c r="E40" s="46"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H36" s="48"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="46" t="s">
+      <c r="H40" s="47"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M40" s="45"/>
+      <c r="N40" s="45"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="46" t="s">
+      <c r="B41" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="46" t="s">
+      <c r="C41" s="45" t="s">
         <v>793</v>
       </c>
-      <c r="D37" s="46" t="s">
+      <c r="D41" s="45" t="s">
         <v>793</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46" t="s">
+      <c r="E41" s="46"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H37" s="48"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="46" t="s">
+      <c r="H41" s="47"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="45"/>
+      <c r="N41" s="45"/>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B42" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="46" t="s">
+      <c r="C42" s="45" t="s">
         <v>794</v>
       </c>
-      <c r="D38" s="46" t="s">
+      <c r="D42" s="45" t="s">
         <v>794</v>
       </c>
-      <c r="E38" s="47"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46" t="s">
+      <c r="E42" s="46"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H38" s="48"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="46" t="s">
+      <c r="H42" s="47"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="46" t="s">
+      <c r="B43" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C39" s="46" t="s">
+      <c r="C43" s="45" t="s">
         <v>795</v>
       </c>
-      <c r="D39" s="46" t="s">
+      <c r="D43" s="45" t="s">
         <v>795</v>
       </c>
-      <c r="E39" s="47"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46" t="s">
+      <c r="E43" s="46"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H39" s="48"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-      <c r="L39" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="46" t="s">
+      <c r="H43" s="47"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="45"/>
+      <c r="N43" s="45"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="46" t="s">
+      <c r="B44" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="46" t="s">
+      <c r="C44" s="45" t="s">
         <v>796</v>
       </c>
-      <c r="D40" s="46" t="s">
+      <c r="D44" s="45" t="s">
         <v>796</v>
       </c>
-      <c r="E40" s="47"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46" t="s">
+      <c r="E44" s="46"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H40" s="48"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="46" t="s">
+      <c r="H44" s="47"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="45"/>
+      <c r="N44" s="45"/>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="46" t="s">
+      <c r="B45" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="46" t="s">
+      <c r="C45" s="45" t="s">
         <v>797</v>
       </c>
-      <c r="D41" s="46" t="s">
+      <c r="D45" s="45" t="s">
         <v>797</v>
       </c>
-      <c r="E41" s="47"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="46" t="s">
+      <c r="E45" s="46"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H41" s="48"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
-      <c r="L41" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="46" t="s">
+      <c r="H45" s="47"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" s="45"/>
+      <c r="N45" s="45"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B46" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="46" t="s">
+      <c r="C46" s="45" t="s">
         <v>798</v>
       </c>
-      <c r="D42" s="46" t="s">
+      <c r="D46" s="45" t="s">
         <v>798</v>
       </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46" t="s">
+      <c r="E46" s="46"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H42" s="48"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="46" t="s">
+      <c r="H46" s="47"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" s="45"/>
+      <c r="N46" s="45"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="46" t="s">
+      <c r="B47" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="46" t="s">
+      <c r="C47" s="45" t="s">
         <v>799</v>
       </c>
-      <c r="D43" s="46" t="s">
+      <c r="D47" s="45" t="s">
         <v>799</v>
       </c>
-      <c r="E43" s="47"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46" t="s">
+      <c r="E47" s="46"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H43" s="48"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="46" t="s">
+      <c r="H47" s="47"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="46" t="s">
+      <c r="B48" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="46" t="s">
+      <c r="C48" s="45" t="s">
         <v>800</v>
       </c>
-      <c r="D44" s="46" t="s">
+      <c r="D48" s="45" t="s">
         <v>800</v>
       </c>
-      <c r="E44" s="47"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46" t="s">
+      <c r="E48" s="46"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H44" s="48"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="46" t="s">
+      <c r="H48" s="47"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B49" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="46" t="s">
+      <c r="C49" s="45" t="s">
         <v>801</v>
       </c>
-      <c r="D45" s="46" t="s">
+      <c r="D49" s="45" t="s">
         <v>801</v>
       </c>
-      <c r="E45" s="47"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46" t="s">
+      <c r="E49" s="46"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H45" s="48"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="46" t="s">
+      <c r="H49" s="47"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M49" s="45"/>
+      <c r="N49" s="45"/>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="46" t="s">
+      <c r="B50" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="46" t="s">
+      <c r="C50" s="45" t="s">
         <v>802</v>
       </c>
-      <c r="D46" s="46" t="s">
+      <c r="D50" s="45" t="s">
         <v>802</v>
       </c>
-      <c r="E46" s="47"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46" t="s">
+      <c r="E50" s="46"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H46" s="48"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="46" t="s">
+      <c r="H50" s="47"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45"/>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B51" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="46" t="s">
+      <c r="C51" s="45" t="s">
         <v>803</v>
       </c>
-      <c r="D47" s="46" t="s">
+      <c r="D51" s="45" t="s">
         <v>803</v>
       </c>
-      <c r="E47" s="47"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46" t="s">
+      <c r="E51" s="46"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="H47" s="48"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="46"/>
-      <c r="L47" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B48" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="46" t="s">
-        <v>804</v>
-      </c>
-      <c r="D48" s="46" t="s">
-        <v>804</v>
-      </c>
-      <c r="E48" s="47"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="H48" s="48"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="46" t="s">
-        <v>805</v>
-      </c>
-      <c r="D49" s="46" t="s">
-        <v>805</v>
-      </c>
-      <c r="E49" s="47"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="H49" s="48"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="46" t="s">
-        <v>806</v>
-      </c>
-      <c r="D50" s="46" t="s">
-        <v>806</v>
-      </c>
-      <c r="E50" s="47"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="H50" s="48"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="46" t="s">
-        <v>807</v>
-      </c>
-      <c r="D51" s="46" t="s">
-        <v>807</v>
-      </c>
-      <c r="E51" s="47"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="H51" s="48"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" s="45"/>
+      <c r="N51" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21146,10 +21120,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -21160,15 +21134,15 @@
         <v>12</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -21186,15 +21160,15 @@
         <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -21212,15 +21186,15 @@
         <v>12</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -21238,15 +21212,15 @@
         <v>12</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -21264,15 +21238,15 @@
         <v>12</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -21524,10 +21498,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -22837,7 +22811,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C33AF5E-A734-41CA-9EFE-DDEA6876FF54}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -22845,70 +22819,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="43" t="s">
-        <v>819</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>820</v>
+      <c r="A1" s="42" t="s">
+        <v>813</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>12</v>
+      <c r="A2" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>12</v>
+      <c r="A3" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>71</v>
+      <c r="A4" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="43" t="s">
-        <v>822</v>
-      </c>
-      <c r="B8" s="43" t="s">
+      <c r="A5" s="42" t="s">
+        <v>816</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F6BA15-EC86-40B3-ABAC-AE5B11920CB2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22969,10 +22928,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -24397,1082 +24356,1078 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="45" t="s">
-        <v>818</v>
-      </c>
-      <c r="N1" s="45" t="s">
-        <v>817</v>
-      </c>
-      <c r="O1" s="31" t="s">
-        <v>818</v>
-      </c>
-      <c r="P1" s="31" t="s">
-        <v>817</v>
-      </c>
+      <c r="M1" s="44" t="s">
+        <v>812</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>811</v>
+      </c>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="46" t="s">
+      <c r="A2" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46" t="s">
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="46" t="s">
+      <c r="A3" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="46" t="s">
+      <c r="A5" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46" t="s">
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46" t="s">
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="A6" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46" t="s">
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46" t="s">
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="46" t="s">
+      <c r="A7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46" t="s">
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="46" t="s">
+      <c r="A8" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46" t="s">
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46" t="s">
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="46" t="s">
+      <c r="A9" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46" t="s">
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46" t="s">
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="46" t="s">
+      <c r="A10" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46" t="s">
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="46" t="s">
+      <c r="A11" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46" t="s">
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="46" t="s">
+      <c r="A12" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46" t="s">
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46" t="s">
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="46" t="s">
+      <c r="A13" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46" t="s">
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="46" t="s">
+      <c r="A14" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46" t="s">
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="46" t="s">
+      <c r="A15" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46" t="s">
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46" t="s">
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="46" t="s">
+      <c r="A16" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46" t="s">
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46" t="s">
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="46" t="s">
+      <c r="A17" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46" t="s">
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="46" t="s">
+      <c r="A18" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="45" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="45" t="s">
         <v>217</v>
       </c>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46" t="s">
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46" t="s">
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="46" t="s">
+      <c r="A19" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46" t="s">
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46" t="s">
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="46" t="s">
+      <c r="A20" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46" t="s">
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="46" t="s">
+      <c r="A21" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46" t="s">
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="46" t="s">
+      <c r="A22" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46" t="s">
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46" t="s">
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="46" t="s">
+      <c r="A23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="46" t="s">
+      <c r="A24" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46" t="s">
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="46" t="s">
+      <c r="A25" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46" t="s">
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46" t="s">
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="46" t="s">
+      <c r="A26" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46" t="s">
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46" t="s">
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="46" t="s">
+      <c r="A27" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46" t="s">
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="46" t="s">
+      <c r="A28" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46" t="s">
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46" t="s">
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="46" t="s">
+      <c r="A29" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46" t="s">
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46" t="s">
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="46" t="s">
+      <c r="A30" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D30" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46" t="s">
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="46" t="s">
+      <c r="A31" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46" t="s">
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="46" t="s">
+      <c r="A32" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46" t="s">
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46" t="s">
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="46" t="s">
+      <c r="A33" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46" t="s">
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="46" t="s">
+      <c r="A34" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="46" t="s">
+      <c r="D34" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46" t="s">
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="46" t="s">
+      <c r="A35" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D35" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="50" t="s">
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="50" t="s">
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+      <c r="M35" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="N35" s="46" t="s">
+      <c r="N35" s="45" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="46" t="s">
+      <c r="A36" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="50" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="46"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="50" t="s">
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="N36" s="46" t="s">
+      <c r="N36" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="46" t="s">
+      <c r="A37" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="D37" s="46" t="s">
+      <c r="D37" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="50" t="s">
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="N37" s="46" t="s">
+      <c r="N37" s="45" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="46"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25534,10 +25489,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -26902,10 +26857,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -28560,10 +28515,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -29881,6 +29836,7 @@
     <col min="9" max="9" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15">
@@ -29921,10 +29877,10 @@
         <v>11</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:14">
